--- a/Pruebas calificadas/COLEGIO-GIMNASIO-SABIO-CALDAS-(IED)-901_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-GIMNASIO-SABIO-CALDAS-(IED)-901_CALIFICADO.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>MATEMÁTICAS</t>
+          <t>LENGUAJE</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1870,9 +1870,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1880,9 +1880,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1900,9 +1900,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1910,9 +1910,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1920,9 +1920,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1950,9 +1950,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1960,9 +1960,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
@@ -1970,9 +1970,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AG6" s="2" t="inlineStr">
@@ -1990,9 +1990,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AJ6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AJ6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AK6" s="2" t="inlineStr">
@@ -2000,9 +2000,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AL6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AM6" s="2" t="inlineStr">
@@ -2020,9 +2020,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="AP6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AQ6" s="2" t="inlineStr">
@@ -2030,9 +2030,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="AR6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AS6" s="2" t="inlineStr">
@@ -2040,9 +2040,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="AT6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AU6" s="2" t="inlineStr">
@@ -2050,9 +2050,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="AV6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AW6" s="5">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8165,7 +8165,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>LENGUAJE</t>
+          <t>MATEMÁTICAS</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -8183,9 +8183,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
@@ -8193,9 +8193,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -8213,9 +8213,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="R31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -8223,9 +8223,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="T31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8263,9 +8263,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB31" s="3" t="inlineStr">
-        <is>
-          <t>CORRECTO</t>
+      <c r="AB31" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -8273,9 +8273,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AD31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AD31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AE31" s="2" t="inlineStr">
@@ -8283,9 +8283,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AF31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AG31" s="2" t="inlineStr">
@@ -8303,9 +8303,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="AJ31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AJ31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AK31" s="2" t="inlineStr">
@@ -8313,9 +8313,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AL31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AM31" s="2" t="inlineStr">
@@ -8333,9 +8333,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AP31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AQ31" s="2" t="inlineStr">
@@ -8343,9 +8343,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="AR31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AS31" s="2" t="inlineStr">
@@ -8353,9 +8353,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AT31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AU31" s="2" t="inlineStr">
@@ -8363,9 +8363,9 @@
           <t>B</t>
         </is>
       </c>
-      <c r="AV31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AW31" s="5">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15461,7 +15461,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16220,7 +16220,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16726,7 +16726,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17232,7 +17232,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17991,7 +17991,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18244,7 +18244,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-GIMNASIO-SABIO-CALDAS-(IED)-901_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-GIMNASIO-SABIO-CALDAS-(IED)-901_CALIFICADO.xlsx
@@ -1191,9 +1191,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1697,9 +1697,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -2709,9 +2709,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -3215,9 +3215,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB11" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -3468,9 +3468,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB12" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -5235,9 +5235,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB19" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -5741,9 +5741,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB21" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -6247,9 +6247,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB23" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -6749,9 +6749,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB25" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -7251,9 +7251,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB27" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -7757,9 +7757,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB29" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -8263,9 +8263,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB31" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -8769,9 +8769,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB33" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -9275,9 +9275,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB35" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -11295,9 +11295,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB43" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -11801,9 +11801,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB45" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -13813,9 +13813,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB53" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -15327,9 +15327,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB59" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -15833,9 +15833,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB61" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB61" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -16845,9 +16845,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB65" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB65" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -18363,9 +18363,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB71" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB71" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-GIMNASIO-SABIO-CALDAS-(IED)-901_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-GIMNASIO-SABIO-CALDAS-(IED)-901_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -3349,7 +3305,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3590,11 +3546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -3602,7 +3554,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3843,11 +3795,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -3855,7 +3803,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4092,11 +4040,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -4104,7 +4048,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4345,11 +4289,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -4357,7 +4297,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4598,11 +4538,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -4610,7 +4546,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4851,11 +4787,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -4863,7 +4795,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5104,11 +5036,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -5116,7 +5044,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5357,11 +5285,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -5369,7 +5293,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5610,11 +5534,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -5622,7 +5542,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5863,11 +5783,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -5875,7 +5791,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6116,11 +6032,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -6128,7 +6040,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6369,11 +6281,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -6381,7 +6289,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6618,11 +6526,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -6630,7 +6534,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6871,11 +6775,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -6883,7 +6783,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7120,11 +7020,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -7132,7 +7028,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7373,11 +7269,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -7385,7 +7277,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7626,11 +7518,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -7638,7 +7526,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7879,11 +7767,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -7891,7 +7775,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8132,11 +8016,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -8144,7 +8024,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8385,11 +8265,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -8397,7 +8273,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8638,11 +8514,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -8650,7 +8522,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8891,11 +8763,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -8903,7 +8771,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9144,11 +9012,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -9156,7 +9020,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9397,11 +9261,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -9409,7 +9269,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9650,11 +9510,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -9662,7 +9518,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9903,11 +9759,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -9915,7 +9767,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10156,11 +10008,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -10168,7 +10016,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10409,11 +10257,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -10421,7 +10265,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10658,11 +10502,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -10670,7 +10510,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10911,11 +10751,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -10923,7 +10759,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11164,11 +11000,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -11176,7 +11008,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11417,11 +11249,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -11429,7 +11257,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11670,11 +11498,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -11682,7 +11506,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11923,11 +11747,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -11935,7 +11755,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12176,11 +11996,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -12188,7 +12004,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12429,11 +12245,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -12441,7 +12253,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12682,11 +12494,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -12694,7 +12502,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12935,11 +12743,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -12947,7 +12751,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13176,11 +12980,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -13188,7 +12988,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13429,11 +13229,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -13441,7 +13237,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13682,11 +13478,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -13694,7 +13486,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13935,11 +13727,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -13947,7 +13735,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14188,11 +13976,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -14200,7 +13984,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14441,11 +14225,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -14453,7 +14233,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14694,11 +14474,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -14706,7 +14482,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14947,11 +14723,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -14959,7 +14731,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15196,11 +14968,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -15208,7 +14976,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15449,11 +15217,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -15461,7 +15225,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15702,11 +15466,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -15714,7 +15474,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15955,11 +15715,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -15967,7 +15723,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16208,11 +15964,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -16220,7 +15972,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16461,11 +16213,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -16473,7 +16221,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16714,11 +16462,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -16726,7 +16470,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16967,11 +16711,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -16979,7 +16719,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17220,11 +16960,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -17232,7 +16968,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17473,11 +17209,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -17485,7 +17217,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17726,11 +17458,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -17738,7 +17466,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17979,11 +17707,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -17991,7 +17715,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18232,11 +17956,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001100021</t>
@@ -18244,7 +17964,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO GIMNASIO SABIO CALDAS (IED)</t>
+          <t>COLEGIO GIMNASIO SABIO CALDAS (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
